--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>92.2</v>
+        <v>95.27</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>7.8</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>43.04</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>56.96</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>20.17</v>
+        <v>18.72</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>95.27</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>4.73</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>95.48</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>4.52</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>46.68</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>53.32</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>18.72</v>
+        <v>11.87</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>92.5</v>
+        <v>92.48999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>7.5</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>92.48999999999999</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>7.51</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>71.95999999999999</v>
+        <v>74.08</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>28.04</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>11.87</v>
+        <v>11.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>93.45</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>6.55</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>74.08</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>25.92</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>11.59</v>
+        <v>11.31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>93.02</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>6.98</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>93.26000000000001</v>
+        <v>94.13</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>6.74</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>74.86</v>
+        <v>75.44</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>25.14</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>11.31</v>
+        <v>10.67</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>75.44</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>24.56</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>10.67</v>
+        <v>10.42</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>94.13</v>
+        <v>94.98</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>5.87</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>75.98999999999999</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>24.01</v>
+        <v>34.63</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>10.42</v>
+        <v>12.88</v>
       </c>
     </row>
   </sheetData>
